--- a/측정비_입금정보_업로드_20260126.xlsx
+++ b/측정비_입금정보_업로드_20260126.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Desktop\cursor\측정일지_html\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475785D2-4035-4891-B09F-71C5958BB703}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB089D6-8B85-4401-9E70-A44BDBBF25DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="입금정보일괄업로드양식_20260126입금최종" sheetId="1" r:id="rId1"/>
